--- a/data/trans_dic/P57B3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57B3_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,35</t>
+          <t>7,03; 12,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,52</t>
+          <t>6,89; 11,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,66</t>
+          <t>7,54; 11,2</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,11</t>
+          <t>6,69; 11,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,5</t>
+          <t>7,76; 12,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,86</t>
+          <t>7,71; 11,11</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 77,81</t>
+          <t>9,12; 14,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 20,15</t>
+          <t>11,27; 19,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 71,18</t>
+          <t>10,42; 15,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 14,85</t>
+          <t>11,16; 15,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,4</t>
+          <t>8,06; 11,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,85</t>
+          <t>10,29; 12,95</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 21,24</t>
+          <t>14,94; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,25</t>
+          <t>17,41; 22,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 19,28</t>
+          <t>17,15; 21,18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,46</t>
+          <t>2,1; 9,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,33; 17,64</t>
+          <t>13,52; 17,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,88</t>
+          <t>11,17; 15,01</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 40,68</t>
+          <t>10,98; 13,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,24</t>
+          <t>12,66; 14,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 25,55</t>
+          <t>12,14; 13,55</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83286</t>
+          <t>96974</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34569; 62292</t>
+          <t>38630; 66653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28057; 47077</t>
+          <t>33645; 57315</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68804; 101437</t>
+          <t>78281; 116195</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38521</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>42414</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75520</t>
+          <t>85274</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28220; 50260</t>
+          <t>32350; 55711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28789; 47614</t>
+          <t>32687; 53127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61505; 90483</t>
+          <t>69735; 100464</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>294924</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321021</t>
+          <t>83661</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71448; 519960</t>
+          <t>43002; 70620</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19455; 33632</t>
+          <t>21124; 35952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102070; 594460</t>
+          <t>68704; 100654</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>132017</t>
+          <t>147648</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73642</t>
+          <t>83711</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>231360</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>112694; 153520</t>
+          <t>126209; 171693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40162; 101762</t>
+          <t>69444; 100429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138706; 238485</t>
+          <t>205036; 257895</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>139315</t>
+          <t>163344</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222834</t>
+          <t>266461</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69189; 100878</t>
+          <t>84877; 121735</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104112; 161650</t>
+          <t>144383; 182390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186068; 253517</t>
+          <t>239544; 295904</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>116917</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126052</t>
+          <t>141081</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4290; 22759</t>
+          <t>4972; 22108</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>101193; 133886</t>
+          <t>113828; 149765</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>109275; 148719</t>
+          <t>120587; 161946</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>603793</t>
+          <t>411059</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>430578</t>
+          <t>493750</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034371</t>
+          <t>904809</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>374956; 1372590</t>
+          <t>377646; 451872</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>343304; 473143</t>
+          <t>459497; 528018</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>788780; 1774533</t>
+          <t>858404; 957747</t>
         </is>
       </c>
     </row>
